--- a/data/S1979_80_FINAL.xlsx
+++ b/data/S1979_80_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +80,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12969,7 +12987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13013,6 +13031,64 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1979_80_0037 'Spartak ZŤS Dubnica nad Váhom' prev→CLUB_S1978_79_0029 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1979_80_0058 'Gumárne 1. mája Púchov' prev→CLUB_S1978_79_0079 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0013</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1979_80_0013 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1979_80_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0014</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1979_80_0014 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1979_80_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -43614,6 +43690,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0037</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0037 'Spartak ZŤS Dubnica nad Váhom' prev→CLUB_S1978_79_0029 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0058</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0058 'Gumárne 1. mája Púchov' prev→CLUB_S1978_79_0079 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0013</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1979_80_0013 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1979_80_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0014</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1979_80_0014 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1979_80_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1979_80_FINAL.xlsx
+++ b/data/S1979_80_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12987,7 +12987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13037,7 +13037,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1979_80_0037 'Spartak ZŤS Dubnica nad Váhom' prev→CLUB_S1978_79_0029 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -13049,7 +13049,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1979_80_0058 'Gumárne 1. mája Púchov' prev→CLUB_S1978_79_0079 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -13059,14 +13059,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1979_80_0013</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1979_80_0013 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1979_80_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -13076,17 +13071,516 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1979_80_0014</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1979_80_0014 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1979_80_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0029 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0079 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ZTS Sigma Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -19366,12 +19860,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -19581,12 +20075,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -19979,12 +20473,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -20330,12 +20824,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -20424,12 +20918,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -20471,12 +20965,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -20518,12 +21012,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -20612,12 +21106,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -20864,12 +21358,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -20995,12 +21489,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -21079,12 +21573,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -21625,12 +22119,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -21672,12 +22166,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -22809,12 +23303,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -23647,12 +24141,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -25015,12 +25509,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -25272,12 +25766,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -25492,12 +25986,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -25801,12 +26295,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -26350,12 +26844,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -26768,12 +27262,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -26815,12 +27309,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -28262,12 +28756,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -29065,12 +29559,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Cheb = TJ Lokomotiva depo Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Lokomotivni depo Cheb** = železničárský klub (drive vyznamne pohranicni depo, nejdulezitejsi prepojeni s NSR). city Cheb.</t>
+          <t>Cheb = TJ Lokomotiva depo Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Lokomotivni depo Cheb** = železničárský klub (drive vyznamne pohranicni depo, nejdulezitejsi prepojeni s NSR). city Cheb. || TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Lokomotiva depo Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -29789,12 +30283,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín.</t>
+          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Technické služby Děčín</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
@@ -30701,12 +31195,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov.</t>
+          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov. || TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Důl Jana Žižky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -31030,12 +31524,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov.</t>
+          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov. || TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>SSM Statky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -31465,12 +31959,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Teplice = TJ Sklo Union Teplice (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Sklo Union** = sklarsky koncern (drive Sklarny Teplice, dnes AGC - Asahi Glass Company). city Teplice.</t>
+          <t>Teplice = TJ Sklo Union Teplice (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Sklo Union** = sklarsky koncern (drive Sklarny Teplice, dnes AGC - Asahi Glass Company). city Teplice. || TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Sklo Union Teplice</t>
+          <t>Teplice</t>
         </is>
       </c>
     </row>
@@ -31559,12 +32053,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -32313,12 +32807,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -34118,12 +34612,12 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Pardubice = TJ SSM SNV Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **SSM** = Socialistický svaz mládeže, **SNV** = pravdepodobne 'Sbor narodni bezpecnosti' (= SNB - policejni klub). city Pardubice.</t>
+          <t>Pardubice = TJ SSM SNV Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **SSM** = Socialistický svaz mládeže, **SNV** = pravdepodobne 'Sbor narodni bezpecnosti' (= SNB - policejni klub). city Pardubice. || TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>SSM SNV Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -34244,12 +34738,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Pardubice = TJ Povodí Labe Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Povodí Labe** = státní podnik (správa labské vodní cesty). city Pardubice.</t>
+          <t>Pardubice = TJ Povodí Labe Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Povodí Labe** = státní podnik (správa labské vodní cesty). city Pardubice. || TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Povodí Labe Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -35347,12 +35841,12 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -36499,12 +36993,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -37748,12 +38242,12 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -38047,12 +38541,12 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek. || TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>VP Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -38571,12 +39065,12 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm.</t>
+          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm. || TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>MEZ Frenštát</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -38660,12 +39154,12 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Olomouc = TJ ZTS Sigma Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (district '(OLO)' potvrzen). **ZTS Sigma** = Sigma + ZTS (slouceny - cerpadla a vodni technika). city Olomouc.</t>
+          <t>Olomouc = TJ ZTS Sigma Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj (district '(OLO)' potvrzen). **ZTS Sigma** = Sigma + ZTS (slouceny - cerpadla a vodni technika). city Olomouc. || TBD: city 'ZTS Sigma Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>ZTS Sigma Olomouc</t>
+          <t>Olomouc</t>
         </is>
       </c>
     </row>
@@ -39110,12 +39604,12 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>Olomouc = TJ Sigma ZTS Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Stejne jako ZTS Sigma - jiny poradi slov. city Olomouc.</t>
+          <t>Olomouc = TJ Sigma ZTS Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Stejne jako ZTS Sigma - jiny poradi slov. city Olomouc. || TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>Sigma ZTS Olomouc</t>
+          <t>Olomouc</t>
         </is>
       </c>
     </row>
@@ -43696,11 +44190,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -43745,21 +44239,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0037</t>
+          <t>CLUB_S1979_80_0008</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0037 'Spartak ZŤS Dubnica nad Váhom' prev→CLUB_S1978_79_0029 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -43767,21 +44259,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0058</t>
+          <t>CLUB_S1979_80_0013</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0058 'Gumárne 1. mája Púchov' prev→CLUB_S1978_79_0079 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -43789,21 +44279,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1979_80_0013</t>
+          <t>CLUB_S1979_80_0022</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1979_80_0013 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1979_80_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -43811,24 +44299,862 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1979_80_0014</t>
+          <t>CLUB_S1979_80_0030</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1979_80_0014 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1979_80_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0032</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0033</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0034</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0036</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0037</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0029 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0042</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0045</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0047</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0058</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0079 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0061</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0062</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0089</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0108</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0137</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0144</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0149</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0156</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0156</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0168</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0177</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0178</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0210</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0229</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0244</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0247</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0268</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0275</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0285</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0287</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0300</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0305</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0317</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0345</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0348</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0371</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0374</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0400</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0429</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0436</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0448</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0450</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ZTS Sigma Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1979_80_0460</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1979_80_FINAL.xlsx
+++ b/data/S1979_80_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12987,7 +12987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13037,7 +13037,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -13049,7 +13049,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -13061,7 +13061,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -13073,7 +13073,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -13085,7 +13085,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0029 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -13097,7 +13097,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -13109,7 +13109,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -13121,7 +13121,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0079 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13133,7 +13133,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0029 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13145,7 +13145,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -13157,7 +13157,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -13169,7 +13169,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -13181,7 +13181,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0079 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -13193,7 +13193,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -13205,7 +13205,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -13217,7 +13217,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -13229,7 +13229,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -13241,7 +13241,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -13265,7 +13265,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -13277,7 +13277,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -13289,7 +13289,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -13301,7 +13301,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -13313,7 +13313,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -13325,7 +13325,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -13337,7 +13337,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -13349,7 +13349,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -13361,7 +13361,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -13373,7 +13373,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -13385,7 +13385,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -13397,7 +13397,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -13409,7 +13409,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -13421,7 +13421,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -13433,7 +13433,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -13445,7 +13445,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -13457,7 +13457,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -13469,7 +13469,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ZTS Sigma Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -13481,106 +13481,10 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ZTS Sigma Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -13597,7 +13501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13656,6 +13560,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13698,6 +13607,11 @@
           <t>12 týmů, jeden stůl. Mistr: Poldi SONP Kladno.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13787,6 +13701,11 @@
           <t>I.ČNHL (2 skupiny po 12 + finále) + I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13829,6 +13748,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13871,6 +13795,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13913,6 +13842,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13955,6 +13889,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13995,6 +13934,11 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0008</t>
         </is>
       </c>
     </row>
@@ -19860,12 +19804,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -20473,12 +20417,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -20824,12 +20768,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -21012,12 +20956,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -21358,12 +21302,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -26295,12 +26239,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -35841,12 +35785,12 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -38242,12 +38186,12 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -44190,7 +44134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -44244,12 +44188,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0008</t>
+          <t>CLUB_S1979_80_0013</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44264,12 +44208,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0013</t>
+          <t>CLUB_S1979_80_0032</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44284,12 +44228,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0022</t>
+          <t>CLUB_S1979_80_0033</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44304,12 +44248,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0030</t>
+          <t>CLUB_S1979_80_0036</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44324,12 +44268,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0032</t>
+          <t>CLUB_S1979_80_0037</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0029 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -44344,12 +44288,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0033</t>
+          <t>CLUB_S1979_80_0045</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44364,12 +44308,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0034</t>
+          <t>CLUB_S1979_80_0047</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44384,12 +44328,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0036</t>
+          <t>CLUB_S1979_80_0058</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0079 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -44404,12 +44348,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0037</t>
+          <t>CLUB_S1979_80_0061</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0029 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44424,12 +44368,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0042</t>
+          <t>CLUB_S1979_80_0062</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44444,12 +44388,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0045</t>
+          <t>CLUB_S1979_80_0089</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44464,12 +44408,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0047</t>
+          <t>CLUB_S1979_80_0108</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44484,12 +44428,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0058</t>
+          <t>CLUB_S1979_80_0137</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0079 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44504,12 +44448,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0061</t>
+          <t>CLUB_S1979_80_0144</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44524,12 +44468,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0062</t>
+          <t>CLUB_S1979_80_0149</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44544,12 +44488,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0089</t>
+          <t>CLUB_S1979_80_0156</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44564,12 +44508,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0108</t>
+          <t>CLUB_S1979_80_0168</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44584,12 +44528,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0137</t>
+          <t>CLUB_S1979_80_0177</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44548,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0144</t>
+          <t>CLUB_S1979_80_0178</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -44624,12 +44568,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0149</t>
+          <t>CLUB_S1979_80_0210</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44644,12 +44588,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0156</t>
+          <t>CLUB_S1979_80_0229</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44664,12 +44608,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0156</t>
+          <t>CLUB_S1979_80_0244</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -44684,12 +44628,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0168</t>
+          <t>CLUB_S1979_80_0247</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44704,12 +44648,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0177</t>
+          <t>CLUB_S1979_80_0268</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44724,12 +44668,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0178</t>
+          <t>CLUB_S1979_80_0275</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44744,12 +44688,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0210</t>
+          <t>CLUB_S1979_80_0285</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44764,12 +44708,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0229</t>
+          <t>CLUB_S1979_80_0287</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44784,12 +44728,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0244</t>
+          <t>CLUB_S1979_80_0300</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -44804,12 +44748,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0247</t>
+          <t>CLUB_S1979_80_0305</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44824,12 +44768,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0268</t>
+          <t>CLUB_S1979_80_0317</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -44844,12 +44788,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0275</t>
+          <t>CLUB_S1979_80_0345</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44864,12 +44808,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0285</t>
+          <t>CLUB_S1979_80_0348</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44884,12 +44828,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0287</t>
+          <t>CLUB_S1979_80_0371</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -44904,12 +44848,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0300</t>
+          <t>CLUB_S1979_80_0400</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44924,12 +44868,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0305</t>
+          <t>CLUB_S1979_80_0436</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44944,12 +44888,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0317</t>
+          <t>CLUB_S1979_80_0448</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44964,12 +44908,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0345</t>
+          <t>CLUB_S1979_80_0450</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'ZTS Sigma Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44984,177 +44928,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1979_80_0348</t>
+          <t>CLUB_S1979_80_0460</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1979_80_0371</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1979_80_0374</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1979_80_0400</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1979_80_0429</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1979_80_0436</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1979_80_0448</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1979_80_0450</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'ZTS Sigma Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1979_80_0460</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F47"/>
+  <autoFilter ref="A1:F39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1979_80_FINAL.xlsx
+++ b/data/S1979_80_FINAL.xlsx
@@ -13501,7 +13501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13563,6 +13563,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1979_80_FINAL.xlsx
+++ b/data/S1979_80_FINAL.xlsx
@@ -13842,6 +13842,16 @@
           <t>NODE_S1979_80_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13856,6 +13866,14 @@
         <is>
           <t>NODE_S1978_79_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -13889,6 +13907,8 @@
           <t>NODE_S1979_80_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13903,6 +13923,14 @@
         <is>
           <t>NODE_S1978_79_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -13936,6 +13964,8 @@
           <t>NODE_S1979_80_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13950,6 +13980,14 @@
         <is>
           <t>NODE_S1978_79_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -14067,6 +14105,8 @@
           <t>NODE_S1979_80_0004</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14081,6 +14121,14 @@
         <is>
           <t>Série Ústí n/L – Gottwaldov 0:2. Případné 3. utkání se mělo hrát v Kolíně.</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -14418,6 +14466,8 @@
           <t>NODE_S1979_80_0016</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14427,6 +14477,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -14502,6 +14560,8 @@
           <t>NODE_S1979_80_0016</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14511,6 +14571,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -15142,6 +15210,12 @@
           <t>NODE_S1979_80_0034</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0038</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15151,6 +15225,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -15226,6 +15308,8 @@
           <t>NODE_S1979_80_0034</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15235,6 +15319,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -15572,6 +15664,16 @@
           <t>NODE_S1979_80_0044</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0047</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0048</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15581,6 +15683,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -15614,6 +15724,8 @@
           <t>NODE_S1979_80_0044</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15623,6 +15735,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -15656,6 +15776,8 @@
           <t>NODE_S1979_80_0044</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15665,6 +15787,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -15955,6 +16085,16 @@
           <t>NODE_S1979_80_0053</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0063</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0059</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15964,6 +16104,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -16123,6 +16271,8 @@
           <t>NODE_S1979_80_0053</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16132,6 +16282,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -16291,6 +16449,8 @@
           <t>NODE_S1979_80_0053</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16300,6 +16460,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -16632,6 +16800,12 @@
           <t>NODE_S1979_80_0069</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0073</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16641,6 +16815,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -16716,6 +16898,8 @@
           <t>NODE_S1979_80_0069</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16725,6 +16909,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>7.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -17613,6 +17805,12 @@
           <t>NODE_S1979_80_0092</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>NODE_S1979_80_0096</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17622,6 +17820,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -17697,6 +17903,8 @@
           <t>NODE_S1979_80_0092</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17706,6 +17914,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="98">

--- a/data/S1979_80_FINAL.xlsx
+++ b/data/S1979_80_FINAL.xlsx
@@ -718,6 +718,11 @@
           <t>TJ Poldi SONP Kladno</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -13907,8 +13912,6 @@
           <t>NODE_S1979_80_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13964,8 +13967,6 @@
           <t>NODE_S1979_80_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14105,8 +14106,6 @@
           <t>NODE_S1979_80_0004</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14466,8 +14465,6 @@
           <t>NODE_S1979_80_0016</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14560,8 +14557,6 @@
           <t>NODE_S1979_80_0016</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15210,7 +15205,6 @@
           <t>NODE_S1979_80_0034</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>NODE_S1979_80_0038</t>
@@ -15308,8 +15302,6 @@
           <t>NODE_S1979_80_0034</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15724,8 +15716,6 @@
           <t>NODE_S1979_80_0044</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15776,8 +15766,6 @@
           <t>NODE_S1979_80_0044</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16271,8 +16259,6 @@
           <t>NODE_S1979_80_0053</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16449,8 +16435,6 @@
           <t>NODE_S1979_80_0053</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16800,7 +16784,6 @@
           <t>NODE_S1979_80_0069</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>NODE_S1979_80_0073</t>
@@ -16898,8 +16881,6 @@
           <t>NODE_S1979_80_0069</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17805,7 +17786,6 @@
           <t>NODE_S1979_80_0092</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>NODE_S1979_80_0096</t>
@@ -17903,8 +17883,6 @@
           <t>NODE_S1979_80_0092</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -41015,7 +40993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41123,6 +41101,18 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>opraveno dle auditu v rozsahu kritických a hlavních vysokých vad</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Poldi SONP Kladno</t>
         </is>
       </c>
     </row>

--- a/data/S1979_80_FINAL.xlsx
+++ b/data/S1979_80_FINAL.xlsx
@@ -52628,7 +52628,7 @@
           <t>CLUB_S1979_80_0013</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52648,7 +52648,7 @@
           <t>CLUB_S1979_80_0032</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52668,7 +52668,7 @@
           <t>CLUB_S1979_80_0033</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52688,7 +52688,7 @@
           <t>CLUB_S1979_80_0036</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52708,7 +52708,7 @@
           <t>CLUB_S1979_80_0037</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0029 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -52728,7 +52728,7 @@
           <t>CLUB_S1979_80_0045</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52748,7 +52748,7 @@
           <t>CLUB_S1979_80_0047</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52768,7 +52768,7 @@
           <t>CLUB_S1979_80_0058</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1978_79_0079 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -52788,7 +52788,7 @@
           <t>CLUB_S1979_80_0061</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52808,7 +52808,7 @@
           <t>CLUB_S1979_80_0062</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52828,7 +52828,7 @@
           <t>CLUB_S1979_80_0089</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -52848,7 +52848,7 @@
           <t>CLUB_S1979_80_0108</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52868,7 +52868,7 @@
           <t>CLUB_S1979_80_0137</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52888,7 +52888,7 @@
           <t>CLUB_S1979_80_0144</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52908,7 +52908,7 @@
           <t>CLUB_S1979_80_0149</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -52928,7 +52928,7 @@
           <t>CLUB_S1979_80_0156</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52948,7 +52948,7 @@
           <t>CLUB_S1979_80_0168</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52968,7 +52968,7 @@
           <t>CLUB_S1979_80_0177</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -52988,7 +52988,7 @@
           <t>CLUB_S1979_80_0178</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53008,7 +53008,7 @@
           <t>CLUB_S1979_80_0210</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53028,7 +53028,7 @@
           <t>CLUB_S1979_80_0229</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53048,7 +53048,7 @@
           <t>CLUB_S1979_80_0244</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -53068,7 +53068,7 @@
           <t>CLUB_S1979_80_0247</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53088,7 +53088,7 @@
           <t>CLUB_S1979_80_0268</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53108,7 +53108,7 @@
           <t>CLUB_S1979_80_0275</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53128,7 +53128,7 @@
           <t>CLUB_S1979_80_0285</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53148,7 +53148,7 @@
           <t>CLUB_S1979_80_0287</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53168,7 +53168,7 @@
           <t>CLUB_S1979_80_0300</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -53188,7 +53188,7 @@
           <t>CLUB_S1979_80_0305</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53208,7 +53208,7 @@
           <t>CLUB_S1979_80_0317</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -53228,7 +53228,7 @@
           <t>CLUB_S1979_80_0345</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53248,7 +53248,7 @@
           <t>CLUB_S1979_80_0348</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53268,7 +53268,7 @@
           <t>CLUB_S1979_80_0371</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -53288,7 +53288,7 @@
           <t>CLUB_S1979_80_0400</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53308,7 +53308,7 @@
           <t>CLUB_S1979_80_0436</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53328,7 +53328,7 @@
           <t>CLUB_S1979_80_0448</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -53348,7 +53348,7 @@
           <t>CLUB_S1979_80_0450</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>TBD: city 'ZTS Sigma Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -53368,7 +53368,7 @@
           <t>CLUB_S1979_80_0460</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>

--- a/data/S1979_80_FINAL.xlsx
+++ b/data/S1979_80_FINAL.xlsx
@@ -15960,7 +15960,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30_Praha L30</t>
+          <t>Praha, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30_Praha L30 základní část</t>
+          <t>Praha, 3. úroveň (krajský přebor), základní část</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -16136,7 +16136,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30_Praha L30 finálová skupina</t>
+          <t>Praha, 3. úroveň (krajský přebor) finálová skupina</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30_Praha L30 skupina o 5.-8.místo</t>
+          <t>Praha, 3. úroveň (krajský přebor), skupina o 5.-8.místo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30_Středočeský L30</t>
+          <t>Středočeský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -16270,7 +16270,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 KP II.třídy</t>
+          <t>Středočeský, 3. úroveň (krajský přebor) KP II.třídy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina A</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina B</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina C</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30_Středočeský kvalifikace o KP I.třídy</t>
+          <t>Středočeský kvalifikace o KP I.třídy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -16527,7 +16527,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30_Středočeský Kvalifikace o II.třídu</t>
+          <t>Středočeský Kvalifikace o II.třídu</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina A</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina B</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina C</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Středočeský L30 skupina D</t>
+          <t>Středočeský, 3. úroveň (krajský přebor), skupina D</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -16826,7 +16826,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30 Základní část</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor), Základní část</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30 finálová skupina</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor) finálová skupina</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30 skupina o udržení</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor), skupina o udržení</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30 II.třída</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor) II.třída</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30 skupina A</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -17057,7 +17057,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30_Jihočeský L30 skupina B</t>
+          <t>Jihočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30_Jihočeský o postup do KP</t>
+          <t>Jihočeský o postup do KP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30_Jihočeský kvalifikace o II.třídu</t>
+          <t>Jihočeský kvalifikace o II.třídu</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -17193,7 +17193,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30_Západočeský L30</t>
+          <t>Západočeský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -17235,7 +17235,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Západočeský L30 základní část</t>
+          <t>Západočeský, 3. úroveň (krajský přebor), základní část</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Západočeský L30 finále</t>
+          <t>Západočeský, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Západočeský L30 skupina o udržení</t>
+          <t>Západočeský, 3. úroveň (krajský přebor), skupina o udržení</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Západočeský L30 II.třída</t>
+          <t>Západočeský, 3. úroveň (krajský přebor) II.třída</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -17479,7 +17479,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Západočeský L30 skupina A</t>
+          <t>Západočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Západočeský L30 skupina B</t>
+          <t>Západočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Západočeský kvalifikace o I.třídu</t>
+          <t>Západočeský kvalifikace o I.třídu</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Severočeský L30</t>
+          <t>Severočeský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 základní část</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), základní část</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 skupina A</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 skupina B</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 finálová skupina</t>
+          <t>Severočeský, 3. úroveň (krajský přebor) finálová skupina</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 skupina o udržení</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), skupina o udržení</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 Meziokresní soutěž</t>
+          <t>Severočeský, 3. úroveň (krajský přebor) Meziokresní soutěž</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 skupina A</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 skupina B</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Severočeský L30 finále</t>
+          <t>Severočeský, 3. úroveň (krajský přebor), finále</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Východočeský L30</t>
+          <t>Východočeský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Východočeský L30 skupina A</t>
+          <t>Východočeský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Východočeský L30 skupina B</t>
+          <t>Východočeský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Východočeský kvalifikace</t>
+          <t>Východočeský kvalifikace</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18405,7 +18405,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 Základní část</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), Základní část</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18460,7 +18460,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 finálová skupina</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor) finálová skupina</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina o udržení</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina o udržení</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 II.třída</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor) II.třída</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina A</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 skupina B</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Jihomoravský kvalifikace o KP</t>
+          <t>Jihomoravský kvalifikace o KP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Jihomoravský Kvalifikace o II. Třídu</t>
+          <t>Jihomoravský Kvalifikace o II. Třídu</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -18772,7 +18772,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 1.kolo</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor) 1.kolo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -18814,7 +18814,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L30 2.kolo</t>
+          <t>Jihomoravský, 3. úroveň (krajský přebor) 2.kolo</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 základní skupina</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor), základní skupina</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 finálová skupina</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor) finálová skupina</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 KP II.třídy</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor) KP II.třídy</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 skupina A</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -19108,7 +19108,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 skupina B</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30_Severomoravský Kvalifikace o KP II.třídy</t>
+          <t>Severomoravský Kvalifikace o KP II.třídy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 skupina A</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor), skupina A</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 skupina B</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor), skupina B</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30_Severomoravský L30 skupina C</t>
+          <t>Severomoravský, 3. úroveň (krajský přebor), skupina C</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -19323,7 +19323,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30_SVK L30</t>
+          <t>Slovensko, 3. úroveň (krajský přebor)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30_SVK L30 Západoslovenský kraj</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) Západoslovenský kraj</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -19407,7 +19407,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30_SVK L30 základní skupina</t>
+          <t>Slovensko, 3. úroveň (krajský přebor), základní skupina</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>30_SVK L30 finálová skupina</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) finálová skupina</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30_SVK L30 skupina o udržení</t>
+          <t>Slovensko, 3. úroveň (krajský přebor), skupina o udržení</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30_SVK L30 Středoslovenský kraj</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) Středoslovenský kraj</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30_SVK L30 Východoslovenský kraj</t>
+          <t>Slovensko, 3. úroveň (krajský přebor) Východoslovenský kraj</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">

--- a/data/S1979_80_FINAL.xlsx
+++ b/data/S1979_80_FINAL.xlsx
@@ -3492,7 +3492,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -54838,7 +54838,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -54921,7 +54921,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -55004,7 +55004,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -55082,7 +55082,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -55160,7 +55160,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -55238,7 +55238,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -55316,7 +55316,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -55399,7 +55399,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -63964,7 +63964,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -64047,7 +64047,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -64125,7 +64125,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -64203,7 +64203,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -70635,7 +70635,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -70713,7 +70713,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -70791,7 +70791,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -75695,7 +75695,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -75773,7 +75773,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -75851,7 +75851,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -75929,7 +75929,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -76007,7 +76007,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -76090,7 +76090,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
